--- a/Result/profitability/3548.xlsx
+++ b/Result/profitability/3548.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.23</v>
       </c>
       <c r="M2" t="n">
-        <v>0.60625</v>
+        <v>0.4137499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>12.815</v>
+        <v>11.69875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.55</v>
       </c>
       <c r="M3" t="n">
-        <v>0.53875</v>
+        <v>0.15125</v>
       </c>
       <c r="N3" t="n">
-        <v>13.08</v>
+        <v>12.0125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.86</v>
       </c>
       <c r="M4" t="n">
-        <v>0.44</v>
+        <v>0.2775</v>
       </c>
       <c r="N4" t="n">
-        <v>13.40375</v>
+        <v>12.7425</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.42</v>
+        <v>0.4625</v>
       </c>
       <c r="N5" t="n">
-        <v>13.66125</v>
+        <v>12.8925</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.53</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5850000000000001</v>
+        <v>0.44375</v>
       </c>
       <c r="N6" t="n">
-        <v>14.09</v>
+        <v>13.51375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.58</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5725</v>
+        <v>0.33</v>
       </c>
       <c r="N7" t="n">
-        <v>15.04875</v>
+        <v>14.56</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.16</v>
       </c>
       <c r="M8" t="n">
-        <v>0.53125</v>
+        <v>0.64375</v>
       </c>
       <c r="N8" t="n">
-        <v>16.67125</v>
+        <v>16.51625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.93</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8162499999999999</v>
+        <v>0.81625</v>
       </c>
       <c r="N9" t="n">
         <v>18.45875</v>
@@ -2026,7 +2026,7 @@
         <v>-0.86</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6300000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="N13" t="n">
         <v>19.6825</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3548</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2373</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2210</v>
+      </c>
+      <c r="E75" t="n">
+        <v>163</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-42</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-1.78%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>19</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-23</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-31</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.5212499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>11.69375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.239999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1530864197530863</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.430379746835443</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-6.149999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.4727132974634896</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
